--- a/Báo cáo tồn kho.xlsx
+++ b/Báo cáo tồn kho.xlsx
@@ -1,14 +1,36 @@
+
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet_7_Khánh Hòa" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
+</file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="2">
@@ -19,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -27,12 +49,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -390,4 +422,6486 @@
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O125"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Báo cáo tồn kho: 3MNĐLKH01 ĐL PHẠM THỊ THÚY KIỀU-KHÁNH HÒA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Từ 2025-05-01 đến 2025-05-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Mã sản phẩm</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Tên sản phẩm</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Đơn giá</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Loại hàng hoá</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Tồn kho đầu kỳ (SL)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Tồn kho đầu kỳ (KM)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Số lượng nhập (SL)</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Số lượng nhập (KM)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Doanh số nhập</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Số lượng bán (SL)</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Số lượng bán (KM)</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Doanh số bán</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tồn kho cuối kỳ (SL)</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Tồn kho cuối kỳ (KM)</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Công nợ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FNYMCN0011</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NYMAX (Kiện 150 hộp x 1 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>75000</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TÂN DƯỢC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FFERAA0012.1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TÍCH ĐIỂM_FEROBIPHA - MẪU 2 (Kiện 105 hộp x 6 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>46000</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>230000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FFERAA0012</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FEROBIPHA - MẪU 2 (Kiện 105 hộp x 6 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>46000</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FBGAAA0013.1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TÍCH ĐIỂM_BỔ GAN ABIPHA - MẪU 2 (Kiện 100 hộp x 1 túi x 5 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>65000</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FBGAAA0013</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BỔ GAN ABIPHA - MẪU 2 (Kiện 100 hộp x 1 túi x 5 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>65000</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCALAA0013.1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TÍCH ĐIỂM_CALCI D3 - MẪU 2 (Kiện 100 hộp x 6 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>48000</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H10" t="n">
+        <v>15</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FCALAA0013</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CALCI D3 - MẪU 2 (Kiện 100 hộp x 6 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>48000</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FENTAA0021</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Enterome Gold (Kiện 60 hộp x 4 vỉ x 5 ống x 5ml)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>96000</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 2_TPCN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>480000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>480000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FEURAA0022</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>EUROSCA FORT - MẪU2 (Kiện 100 hộp x 10 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>56000</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FEURAA0022.1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TÍCH ĐIỂM_EUROSCA FORT - MẪU2 (Kiện 100 hộp x 10 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>56000</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FVEAAA0012</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>VITAMIN E ABIPHA - MẪU 2 (Kiện 100 hộp x 1 túi x 3 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>29000</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FVEAAA0012.1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TÍCH ĐIỂM_VITAMIN E ABIPHA - MẪU 2 (Kiện 100 hộp x 1 túi x 3 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>29000</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FVITAA0022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>VITAMIN 3B ABI - MẪU 2 (Kiện 80 hộp 10 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>56000</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FVITAA0022.1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TÍCH ĐIỂM_VITAMIN 3B ABI - MẪU 2 (Kiện 80 hộp 10 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>56000</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FVADAA0013.1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TÍCH ĐIỂM_VITAMIN A-D - MẪU 2 (Kiện 100 hộp x10 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>36000</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FSANAA0012.1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TÍCH ĐIỂM_SIRO ĂN NGON ABIPHA - MẪU 2 (Kiện 60 hộp x 1 lọ 125ml)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>48000</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FVADAA0013</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>VITAMIN A-D - MẪU 2 (Kiện 100 hộp x10 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>36000</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FSANAA0012</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SIRO ĂN NGON ABIPHA - MẪU 2 (Kiện 60 hộp x 1 lọ 125ml)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>48000</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FGCQAA0012.1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TÍCH ĐIỂM_GINKGO 150 COQ10 ABIPHA - MẪU 2 (Kiện 80 Hộp 10 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>75000</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>210</v>
+      </c>
+      <c r="H23" t="n">
+        <v>63</v>
+      </c>
+      <c r="I23" t="n">
+        <v>15750000</v>
+      </c>
+      <c r="J23" t="n">
+        <v>210</v>
+      </c>
+      <c r="K23" t="n">
+        <v>63</v>
+      </c>
+      <c r="L23" t="n">
+        <v>15750000</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>FGCQAA0012</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>GINKGO 150 COQ10 ABIPHA - MẪU 2 (Kiện 80 Hộp 10 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>75000</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>20</v>
+      </c>
+      <c r="H24" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J24" t="n">
+        <v>20</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FVITAA0021</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Vitamin 3B (Kiện 75 hộp x 10 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>56000</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>20</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-32</v>
+      </c>
+      <c r="G25" t="n">
+        <v>165</v>
+      </c>
+      <c r="H25" t="n">
+        <v>33</v>
+      </c>
+      <c r="I25" t="n">
+        <v>9240000</v>
+      </c>
+      <c r="J25" t="n">
+        <v>145</v>
+      </c>
+      <c r="K25" t="n">
+        <v>29</v>
+      </c>
+      <c r="L25" t="n">
+        <v>8120000</v>
+      </c>
+      <c r="M25" t="n">
+        <v>40</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-28</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2240000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>FNKGCN0011.1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TĐ_NGÂN KIỀU GIẢI ĐỘC ABIPHA (Kiện 100 hộp x 1 túi x 3 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>96000</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>FNKGCN0011</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NGÂN KIỀU GIẢI ĐỘC ABIPHA (Kiện 100 hộp x 1 túi x 3 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>96000</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>FOMEAA0021</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>OMEGOLD 369 ABIPHA (kiện 84 hộp x 1lọ x 100viên)</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>118000</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 2_TPCN</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>80</v>
+      </c>
+      <c r="H28" t="n">
+        <v>16</v>
+      </c>
+      <c r="I28" t="n">
+        <v>9440000</v>
+      </c>
+      <c r="J28" t="n">
+        <v>80</v>
+      </c>
+      <c r="K28" t="n">
+        <v>16</v>
+      </c>
+      <c r="L28" t="n">
+        <v>9440000</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>FBRACN0011</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BRAINCULIN 400 (Kiện 100 hộp x 5 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>59000</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TÂN DƯỢC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>FPHAAA0011</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PHARCITON (Kiện 135 x hộp 6 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>46000</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>70</v>
+      </c>
+      <c r="H30" t="n">
+        <v>14</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3220000</v>
+      </c>
+      <c r="J30" t="n">
+        <v>70</v>
+      </c>
+      <c r="K30" t="n">
+        <v>14</v>
+      </c>
+      <c r="L30" t="n">
+        <v>3220000</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>FBTACN0022</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>THUỐC BÀI THẠCH ABIPHA (Kiện 162 hộp x 1 lọ x 30 viên)</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>45000</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>FXHKAA0021</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Xịt họng KEO ONG 15 ML Abipolis KIDS</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>75000</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FBPAAA0021</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BOPHOI ABIPOLIS (Kiện 180 hộp x 1 túi x 6 vỉ x 5 viên)</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>106000</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>150</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>139</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>11</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>FTHBCN0011</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>THUỐC HO BỔ PHỔI ABIPHA (Hộp 1 lọ x 100ml)</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-11</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-11</v>
+      </c>
+      <c r="O34" t="n">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>FVITAA0031</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>VITAMIN 8B (Kiện 75 hộp X 1 Túi x 10 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>73000</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>10</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-26</v>
+      </c>
+      <c r="G35" t="n">
+        <v>70</v>
+      </c>
+      <c r="H35" t="n">
+        <v>14</v>
+      </c>
+      <c r="I35" t="n">
+        <v>5110000</v>
+      </c>
+      <c r="J35" t="n">
+        <v>45</v>
+      </c>
+      <c r="K35" t="n">
+        <v>9</v>
+      </c>
+      <c r="L35" t="n">
+        <v>3285000</v>
+      </c>
+      <c r="M35" t="n">
+        <v>35</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-21</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2555000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>FATACN0012.1</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>TĐ_THUỐC AN THẦN ABIPHA (Kiện 100 hộp x 3 vỉ x 10 viên) (VTT)</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>89000</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>FKCNAA0011</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>KEM CHỐNG NẮNG ABISUN (Kiện 200 hộp x tuýp 50ml)</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>90000</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>FTNHAA0013</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Trinh nữ hoàng cung (Kiện 135 hộp x lọ 30 viên)</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>10</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" t="n">
+        <v>600000</v>
+      </c>
+      <c r="J38" t="n">
+        <v>10</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2</v>
+      </c>
+      <c r="L38" t="n">
+        <v>600000</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>FEURAA0021</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Euroscafort (Kiện 108 hộp x 10 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>56000</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>30</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-75</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>30</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-75</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1680000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>FGINAA0021</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>GINGCOLIN ABIPHA (Kiện 40 Hộp x 1 túi x 10 vỉ x 10 viên )</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>108000</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 2_TPCN</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>FVXACN0011</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>THUỐC VIÊM XOANG ABIPHA CAP. (Kiện 100 hộp x 1 túi x 3 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>86000</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>FHHDAA0011</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Hoạt Huyết Dưỡng Não (Kiện 96 hộp x 1 túi x 5 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>35000</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>15</v>
+      </c>
+      <c r="H42" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" t="n">
+        <v>525000</v>
+      </c>
+      <c r="J42" t="n">
+        <v>15</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3</v>
+      </c>
+      <c r="L42" t="n">
+        <v>525000</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>FBTNAA0011</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Bổ thận nữ ABIPHA(kiện 134 hộp x 3vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>186000</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 2_TPCN</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>42</v>
+      </c>
+      <c r="H43" t="n">
+        <v>14</v>
+      </c>
+      <c r="I43" t="n">
+        <v>7812000</v>
+      </c>
+      <c r="J43" t="n">
+        <v>42</v>
+      </c>
+      <c r="K43" t="n">
+        <v>14</v>
+      </c>
+      <c r="L43" t="n">
+        <v>7812000</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>FCUMAA0011</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CUMMUA ABIPOLIS 50 VIÊN (Kiện 100 hộp x 1 túi x 5 vỉ x 10 viên))</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>56000</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>FHHACN0011</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>THUỐC HOẠT HUYẾT ABIPHA CAP (Kiện 100 hộp x 1 túi x 3 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>105000</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>FXHAAA0013</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>MB - Xịt hong 10 ML abipolis ( Kiện 30h to X 6h bé X 10 ML)</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>58000</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>FVNKAA0012</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>VIÊN NGẬM 100  VIÊN  KEO ONG ABIPOLIS (24h/kiện)</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>190000</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>FTNHAA0011</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Trinh nữ hoàng cung (Kiện 135 hộp x lọ 60 viên)</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>79000</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>FMDGAA0021</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>MIẾNG DÁN GIẢM ĐAU VAI GÁY META (Kiên 100 hộp x 1 túi x 5 miếng)</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>85000</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>FREPCN0041</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>REPITIN (Kiện ... hộp x 1túi x 10 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>165000</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TÂN DƯỢC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>3</v>
+      </c>
+      <c r="H50" t="n">
+        <v>3</v>
+      </c>
+      <c r="I50" t="n">
+        <v>495000</v>
+      </c>
+      <c r="J50" t="n">
+        <v>3</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3</v>
+      </c>
+      <c r="L50" t="n">
+        <v>495000</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>FHHACN0011.1</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>TĐ_THUỐC HOẠT HUYẾT ABIPHA CAP (Kiện 100 hộp x 1 túi x 3 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>105000</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>FHTDCN0011.1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>TĐ_THUỐC HỘ TÂM ĐAN ABIPHA (Kiện 100 hộp x 1 túi x 3 vỉ x 10 viên) (VTT)</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>79000</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>FTDACN0011.1</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>TĐ_THUỐC TIÊU ĐỘC ABIPHA (Kiện 100 hộp x 1 túi x 3 vỉ x 10 viên nén bao phim)</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>118000</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>FTHBCN0011.1</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>TĐ_THUỐC HO BỔ PHỔI ABIPHA (Hộp 1 lọ x 100ml)</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G54" t="n">
+        <v>42</v>
+      </c>
+      <c r="H54" t="n">
+        <v>14</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2520000</v>
+      </c>
+      <c r="J54" t="n">
+        <v>42</v>
+      </c>
+      <c r="K54" t="n">
+        <v>14</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2520000</v>
+      </c>
+      <c r="M54" t="n">
+        <v>3</v>
+      </c>
+      <c r="N54" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O54" t="n">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>FHNTCN0011.1</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>TĐ_Hộ Não Tâm Abipha( Kiện 100 hộp 1 túi 3 vỉ 10 viên)( VTT)</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>139000</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>FVADAA0011</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Vitamin A-D (Kiện 120 hộp x10 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>36000</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>110</v>
+      </c>
+      <c r="H56" t="n">
+        <v>22</v>
+      </c>
+      <c r="I56" t="n">
+        <v>3960000</v>
+      </c>
+      <c r="J56" t="n">
+        <v>110</v>
+      </c>
+      <c r="K56" t="n">
+        <v>22</v>
+      </c>
+      <c r="L56" t="n">
+        <v>3960000</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>FCALAA0021</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CALBIPHA (Kiện 60 hộp x 1 lọ x 60 viên)</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>98000</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 2_TPCN</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>FKDRAA0011</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>KEM ĐÁNH RĂNG KEO ONG ABIPOLIS 100g (55h/kiện)</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>39000</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>FCANAA0021</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CANKE ABIPHA (Kiện 134 hộp x 3 vỉ x 10 viên nang cứng)</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>FXNMAA0011</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Xịt nhiệt miệng ABIPOLIS (Kiện 84 hộp x 1 chai 15ml)</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>65000</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>FNSMAA0021</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Nước súc miệng keo ong ABIPOLIS (Kiện 54 hộp x 1 chai 250ml)</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>39000</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>FFERAA0011</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>FEROBIPHA (Kiện 105 hộp x 6 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>46000</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>10</v>
+      </c>
+      <c r="H62" t="n">
+        <v>2</v>
+      </c>
+      <c r="I62" t="n">
+        <v>460000</v>
+      </c>
+      <c r="J62" t="n">
+        <v>10</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2</v>
+      </c>
+      <c r="L62" t="n">
+        <v>460000</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>FDXAAA0021</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>DƯỠNG XUÂN ABIPHA GOLD ( Kiện 75 Hộp 1 lọ x 30 viên )</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>160000</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 2_TPCN</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>FTKACN0011</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>THUỐC KHỚP ABIPHA (Thùng 100 hộp x 3 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>105000</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>FAGAAA0011</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ARGININ GOLD 400 ABIPHA( Kiện 72 Hộp 2 túi x 6 vỉ x 5 viên)</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>108000</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 2_TPCN</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>175</v>
+      </c>
+      <c r="H65" t="n">
+        <v>35</v>
+      </c>
+      <c r="I65" t="n">
+        <v>18900000</v>
+      </c>
+      <c r="J65" t="n">
+        <v>175</v>
+      </c>
+      <c r="K65" t="n">
+        <v>35</v>
+      </c>
+      <c r="L65" t="n">
+        <v>18900000</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>FEURAA0031</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>EUROSCA MAX ++ (Kiện 108 hộp x 10 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>85000</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>FKTTAA0011</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Kim tiền thảo râu mèo (Kiện 135 hộp x 1 lọ 100 viên)</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>64000</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>FATACN0021</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>THUỐC AN TRÀNG ABIPHA (Kiện 100 hộp x 1 túi x 3 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>82500</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>FDGAAA0011</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Dầu Gấc ABIPHA (Kiện 135 hộp x lọ 100 viên)</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>15</v>
+      </c>
+      <c r="H69" t="n">
+        <v>3</v>
+      </c>
+      <c r="I69" t="n">
+        <v>600000</v>
+      </c>
+      <c r="J69" t="n">
+        <v>10</v>
+      </c>
+      <c r="K69" t="n">
+        <v>2</v>
+      </c>
+      <c r="L69" t="n">
+        <v>400000</v>
+      </c>
+      <c r="M69" t="n">
+        <v>5</v>
+      </c>
+      <c r="N69" t="n">
+        <v>1</v>
+      </c>
+      <c r="O69" t="n">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>FHTDCN0011</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>THUỐC HỘ TÂM ĐAN ABIPHA (Kiện 100 hộp x 1 túi x 3 vỉ x 10 viên) (VTT)</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>79000</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>FCALAA0011</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Calci - D3 (Kiện 135 hộp x 6 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>48000</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>-4</v>
+      </c>
+      <c r="N71" t="n">
+        <v>-4</v>
+      </c>
+      <c r="O71" t="n">
+        <v>-192000</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>FVKAAA0011</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>VIÊN KHỚP ABIPHA (Kiện 108 lọ x 60 viên)</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>95000</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>10</v>
+      </c>
+      <c r="H72" t="n">
+        <v>2</v>
+      </c>
+      <c r="I72" t="n">
+        <v>950000</v>
+      </c>
+      <c r="J72" t="n">
+        <v>10</v>
+      </c>
+      <c r="K72" t="n">
+        <v>2</v>
+      </c>
+      <c r="L72" t="n">
+        <v>950000</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>FBTACN0023</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>THUỐC BÀI THẠCH ABIPHA (Kiện 100 hộp x 3 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>48000</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6</v>
+      </c>
+      <c r="F73" t="n">
+        <v>-24</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>6</v>
+      </c>
+      <c r="N73" t="n">
+        <v>-24</v>
+      </c>
+      <c r="O73" t="n">
+        <v>288000</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>FGDGAA0011</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Giải độc gan Abipolis (Thùng 20 khay nhựa x 10 tuýp x 20 viên sủi 4g)</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>45000</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>FVTAAA0011</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>VƯƠNG TÂM AN ( Kiện 120 Hộp X 3 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>98000</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 2_TPCN</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>FKNEAA0011</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Kẹo ngậm Eurosca (Kiện 6 lọ x 300 viên)</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>139000</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>FATACN0012</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>THUỐC AN THẦN ABIPHA (Kiện 100 hộp x 3 vỉ x 10 viên) (VTT)</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>89000</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>FTNMAA0021</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Thanh nhiệt mát gan Abipha (Kiện 60 hộp x 4 vỉ x 5 ống 10ml)</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>78000</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 2_TPCN</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>15</v>
+      </c>
+      <c r="H78" t="n">
+        <v>3</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1170000</v>
+      </c>
+      <c r="J78" t="n">
+        <v>10</v>
+      </c>
+      <c r="K78" t="n">
+        <v>2</v>
+      </c>
+      <c r="L78" t="n">
+        <v>780000</v>
+      </c>
+      <c r="M78" t="n">
+        <v>5</v>
+      </c>
+      <c r="N78" t="n">
+        <v>1</v>
+      </c>
+      <c r="O78" t="n">
+        <v>390000</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>FEURAA0011</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>EUROSCA  (Kiện 108 hộp x 10 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>36000</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>20</v>
+      </c>
+      <c r="F79" t="n">
+        <v>4</v>
+      </c>
+      <c r="G79" t="n">
+        <v>85</v>
+      </c>
+      <c r="H79" t="n">
+        <v>17</v>
+      </c>
+      <c r="I79" t="n">
+        <v>3060000</v>
+      </c>
+      <c r="J79" t="n">
+        <v>85</v>
+      </c>
+      <c r="K79" t="n">
+        <v>17</v>
+      </c>
+      <c r="L79" t="n">
+        <v>3060000</v>
+      </c>
+      <c r="M79" t="n">
+        <v>20</v>
+      </c>
+      <c r="N79" t="n">
+        <v>4</v>
+      </c>
+      <c r="O79" t="n">
+        <v>720000</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>FSANAA0011</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Siro Ăn Ngon Abipha new* (Kiện 60 hộp x 1 lọ 125ml) - MẪU MỚI</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>48000</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>25</v>
+      </c>
+      <c r="H80" t="n">
+        <v>5</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="J80" t="n">
+        <v>25</v>
+      </c>
+      <c r="K80" t="n">
+        <v>5</v>
+      </c>
+      <c r="L80" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>FHAACN0011</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>THUỐC HẠ ÁP ABIPHA (Kiện 100 hộp x 3 túi x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>98000</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>FTDACN0011</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>THUỐC TIÊU ĐỘC ABIPHA (Kiện 100 hộp x 1 túi x 3 vỉ x 10 viên nén bao phim)</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>118000</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>FHOMAA0011</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Homibipha ginseng (Kiện 108 hộp x 2 túi x 6 vỉ x 5 viên)</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>48000</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>45</v>
+      </c>
+      <c r="H83" t="n">
+        <v>9</v>
+      </c>
+      <c r="I83" t="n">
+        <v>2160000</v>
+      </c>
+      <c r="J83" t="n">
+        <v>45</v>
+      </c>
+      <c r="K83" t="n">
+        <v>9</v>
+      </c>
+      <c r="L83" t="n">
+        <v>2160000</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>FKIDAA0011</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>KIDGOLD ABIPHA (Kiện 60h x 4 vỉ x 5 ống 10ml)</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>92000</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 2_TPCN</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>10</v>
+      </c>
+      <c r="H84" t="n">
+        <v>2</v>
+      </c>
+      <c r="I84" t="n">
+        <v>920000</v>
+      </c>
+      <c r="J84" t="n">
+        <v>10</v>
+      </c>
+      <c r="K84" t="n">
+        <v>2</v>
+      </c>
+      <c r="L84" t="n">
+        <v>920000</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>FVKACN0011</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>THUỐC VIÊN KHỚP ABIPHA (Hộp 1 túi x 3 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>FTNGAA0011</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Thanh nhiệt giải độc Abipha (Kiện 135 hộp x 1 lọ 30V)</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>48000</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>FGLUAA0021</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>GLUTIN 500 ABIPHA (Kiện 135 hộp x 1 túi x 6 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>75000</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F87" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G87" t="n">
+        <v>15</v>
+      </c>
+      <c r="H87" t="n">
+        <v>3</v>
+      </c>
+      <c r="I87" t="n">
+        <v>1125000</v>
+      </c>
+      <c r="J87" t="n">
+        <v>15</v>
+      </c>
+      <c r="K87" t="n">
+        <v>3</v>
+      </c>
+      <c r="L87" t="n">
+        <v>1125000</v>
+      </c>
+      <c r="M87" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N87" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O87" t="n">
+        <v>-75000</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>FKOHAA0011</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SIRO KEO ONG HOABIPOLIS (Kiện 80 hộp x 1 lọ 90ml)</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>48000</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>10</v>
+      </c>
+      <c r="H88" t="n">
+        <v>2</v>
+      </c>
+      <c r="I88" t="n">
+        <v>480000</v>
+      </c>
+      <c r="J88" t="n">
+        <v>10</v>
+      </c>
+      <c r="K88" t="n">
+        <v>2</v>
+      </c>
+      <c r="L88" t="n">
+        <v>480000</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>FTTACN0012</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>THUỐC TIÊU TRĨ ABIPHA (Kiện 100 hộp x 10 gói x 5g)</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>89000</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>FXHAAA0012</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>XỊT HỌNG ABIPOLIS 15 ML   ( KIỆN 198 HỘP x 1CHAI 15 ML15 )</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>75000</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>5</v>
+      </c>
+      <c r="H90" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" t="n">
+        <v>375000</v>
+      </c>
+      <c r="J90" t="n">
+        <v>5</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" t="n">
+        <v>375000</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>FOMEAA0011</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Omega 3 (Kiện 126 hộp x lọ 100 viên)</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>-16</v>
+      </c>
+      <c r="F91" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G91" t="n">
+        <v>510</v>
+      </c>
+      <c r="H91" t="n">
+        <v>102</v>
+      </c>
+      <c r="I91" t="n">
+        <v>40800000</v>
+      </c>
+      <c r="J91" t="n">
+        <v>490</v>
+      </c>
+      <c r="K91" t="n">
+        <v>98</v>
+      </c>
+      <c r="L91" t="n">
+        <v>39200000</v>
+      </c>
+      <c r="M91" t="n">
+        <v>4</v>
+      </c>
+      <c r="N91" t="n">
+        <v>-4</v>
+      </c>
+      <c r="O91" t="n">
+        <v>320000</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>FARGAA0011</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ARGININE (Kiện 108 hộp x 2 túi x 6 vỉ x 5 viên)</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>65000</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>5</v>
+      </c>
+      <c r="H92" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" t="n">
+        <v>325000</v>
+      </c>
+      <c r="J92" t="n">
+        <v>5</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" t="n">
+        <v>325000</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>FHHAAA0021</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Hoạt huyết Abipha (Kiện 134 hộp x 1 túi x 3 vỉ x 10 viên nang cứng)</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>75000</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>FKNEAA0012</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Kẹo ngậm Eurosca (Kiện 48 hộp x 100 viên)</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>68000</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>FGOLAA0021</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>GOLBONES 1500 ABIPHA - (kiện 80 hộp x 1 túi x 6 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>118000</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 2_TPCN</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>255</v>
+      </c>
+      <c r="H95" t="n">
+        <v>51</v>
+      </c>
+      <c r="I95" t="n">
+        <v>30090000</v>
+      </c>
+      <c r="J95" t="n">
+        <v>255</v>
+      </c>
+      <c r="K95" t="n">
+        <v>51</v>
+      </c>
+      <c r="L95" t="n">
+        <v>30090000</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>FANXAA0011</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ANXOANG ABIPHA (Kiện 96 Hộp x 1 lọ 60 viên)</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>89000</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>FKTTAA0012</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Kim tiền thảo râu mèo (Kiện 135 hộp x 1 lọ 60 viên)</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>45000</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F97" t="n">
+        <v>-12</v>
+      </c>
+      <c r="G97" t="n">
+        <v>20</v>
+      </c>
+      <c r="H97" t="n">
+        <v>4</v>
+      </c>
+      <c r="I97" t="n">
+        <v>900000</v>
+      </c>
+      <c r="J97" t="n">
+        <v>10</v>
+      </c>
+      <c r="K97" t="n">
+        <v>2</v>
+      </c>
+      <c r="L97" t="n">
+        <v>450000</v>
+      </c>
+      <c r="M97" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N97" t="n">
+        <v>-10</v>
+      </c>
+      <c r="O97" t="n">
+        <v>-90000</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>FVVGCN0011</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>THUỐC VIÊN VAI GÁY ABIPHA (Kiện 100 hộp x 1 túi x 3 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>128000</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>FDDXAA0011</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Dung dịch xịt mũi-họng NASALDAY (Hộp 1 chai 70ml)</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>39000</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>FDNDAA0011</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Dầu ngải diệp META 50ml (140H/K)</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>38000</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>FEUPCN0011</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>EUPARAKULT EXTRA (Kiện 100 hộp x 10 vỉ x10 viên) (VTT)</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>68000</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TÂN DƯỢC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>5</v>
+      </c>
+      <c r="H101" t="n">
+        <v>1</v>
+      </c>
+      <c r="I101" t="n">
+        <v>340000</v>
+      </c>
+      <c r="J101" t="n">
+        <v>5</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" t="n">
+        <v>340000</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>FGOLAA0012</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Goldbipha new (Kiện 76 hộp x 2 túi x 6 vỉ x 5 viên)</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>138000</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 2_TPCN</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>40</v>
+      </c>
+      <c r="H102" t="n">
+        <v>8</v>
+      </c>
+      <c r="I102" t="n">
+        <v>5520000</v>
+      </c>
+      <c r="J102" t="n">
+        <v>40</v>
+      </c>
+      <c r="K102" t="n">
+        <v>8</v>
+      </c>
+      <c r="L102" t="n">
+        <v>5520000</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>FGCQAA0011</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Ginkgo 150 CoQ10 Abipha (Kiện 80 hộp x 1 túi 10 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>75000</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>10</v>
+      </c>
+      <c r="F103" t="n">
+        <v>2</v>
+      </c>
+      <c r="G103" t="n">
+        <v>50</v>
+      </c>
+      <c r="H103" t="n">
+        <v>10</v>
+      </c>
+      <c r="I103" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="J103" t="n">
+        <v>50</v>
+      </c>
+      <c r="K103" t="n">
+        <v>10</v>
+      </c>
+      <c r="L103" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="M103" t="n">
+        <v>10</v>
+      </c>
+      <c r="N103" t="n">
+        <v>2</v>
+      </c>
+      <c r="O103" t="n">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>FVNKAA0011</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Viên ngậm 20V keo ong Abipolis( Hộp 4 vì x5 Viên x 60h/kiện )</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>46000</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>FXMAAA0011</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Dung Dịch Xịt mũi Abipolis Người Lớn ( Kiện 130 Hộp x1 chai 15ml)</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>29000</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>FBTNAA0021</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Bổ thận Nam ABIPHA (Kiện 134 hộp x 3vỉ x 10viên)</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>186000</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 2_TPCN</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>18</v>
+      </c>
+      <c r="H106" t="n">
+        <v>6</v>
+      </c>
+      <c r="I106" t="n">
+        <v>3348000</v>
+      </c>
+      <c r="J106" t="n">
+        <v>18</v>
+      </c>
+      <c r="K106" t="n">
+        <v>6</v>
+      </c>
+      <c r="L106" t="n">
+        <v>3348000</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>FREPCN0011</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>REPICETYL CAP. (Kiện 100 hộp x 1 túi x 10 vỉ x 10 viên) VTT</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>198000</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TÂN DƯỢC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>-8</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>FLIVAA0011</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>LIVPRO ABIPHA (Kiện 60 Hộp x 1 lọ 60 viên)</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>136000</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 2_TPCN</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>FBGAAA0011</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Bổ Gan ABIPHA (Kiện 96 hộp x 5 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>65000</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>FMDGAA0024</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>MIẾNG DÁN GIẢM ĐAU VAI GÁY META(Kiện 90 hộp x 5 túi x 3 miếng 60*90)</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>FSILAA0011</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SILYGOLD ABIPHA (Kiện 72 hộp x 2 túi x 6 vỉ x 5 viên)</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>128000</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 2_TPCN</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>10</v>
+      </c>
+      <c r="H111" t="n">
+        <v>2</v>
+      </c>
+      <c r="I111" t="n">
+        <v>1280000</v>
+      </c>
+      <c r="J111" t="n">
+        <v>10</v>
+      </c>
+      <c r="K111" t="n">
+        <v>2</v>
+      </c>
+      <c r="L111" t="n">
+        <v>1280000</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>FVEAAA0011</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Vitamin E Abipha (Kiện 135 hộp x 1 túi x 3 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>29000</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_TPCN</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>120</v>
+      </c>
+      <c r="H112" t="n">
+        <v>24</v>
+      </c>
+      <c r="I112" t="n">
+        <v>3480000</v>
+      </c>
+      <c r="J112" t="n">
+        <v>120</v>
+      </c>
+      <c r="K112" t="n">
+        <v>24</v>
+      </c>
+      <c r="L112" t="n">
+        <v>3480000</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>FHNTCN0011</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Hộ Não Tâm Abipha( Kiện 100 hộp 1 túi 3 vỉ 10 viên)( VTT)</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>139000</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>FATACN0021.1</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>TĐ_THUỐC AN TRÀNG ABIPHA (Kiện 100 hộp x 1 túi x 3 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>82500</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>FBTACN0022.1</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>TĐ_THUỐC BÀI THẠCH ABIPHA (Kiện 162 hộp x 1 lọ x 30 viên)</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>48000</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>FBTACN0023.1</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>TĐ_THUỐC BÀI THẠCH ABIPHA (Kiện 100 hộp x 3 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>48000</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="n">
+        <v>3</v>
+      </c>
+      <c r="H116" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" t="n">
+        <v>144000</v>
+      </c>
+      <c r="J116" t="n">
+        <v>3</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1</v>
+      </c>
+      <c r="L116" t="n">
+        <v>144000</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>FHAACN0011.1</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>TĐ_THUỐC HẠ ÁP ABIPHA (Kiện 100 hộp x 3 túi x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>98000</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>FTKACN0011.1</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>TĐ_THUỐC KHỚP ABIPHA (Thùng 100 hộp x 3 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>105000</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>FTTACN0012.1</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>TĐ_THUỐC TIÊU TRĨ ABIPHA (Kiện 100 hộp x 10 gói x 5g)</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>89000</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>FVKACN0011.1</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>TĐ_THUỐC VIÊN KHỚP ABIPHA (Hộp 1 túi x 3 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>FVVGCN0011.1</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>TĐ_THUỐC VIÊN VAI GÁY ABIPHA (Kiện 100 hộp x 1 túi x 3 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>128000</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="n">
+        <v>6</v>
+      </c>
+      <c r="H121" t="n">
+        <v>2</v>
+      </c>
+      <c r="I121" t="n">
+        <v>768000</v>
+      </c>
+      <c r="J121" t="n">
+        <v>6</v>
+      </c>
+      <c r="K121" t="n">
+        <v>2</v>
+      </c>
+      <c r="L121" t="n">
+        <v>768000</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>FVXACN0011.1</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>TĐ_THUỐC VIÊM XOANG ABIPHA CAP. (Kiện 100 hộp x 1 túi x 3 vỉ x 10 viên)</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>86000</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>CKTL</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Chiết khấu tích lũy</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>CKĐH</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Chiết khấu đơn hàng</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>DOIDIEM</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Đổi điểm</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Báo cáo tồn kho.xlsx
+++ b/Báo cáo tồn kho.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet_7_Khánh Hòa" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet_13_Nghệ An" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,7 +436,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Báo cáo tồn kho: 3MNĐLKH01 ĐL PHẠM THỊ THÚY KIỀU-KHÁNH HÒA</t>
+          <t>Báo cáo tồn kho: 1MB8DLNA001 CHỊ THOA - (DÙNG ) DƯỢC PHẨM LINH LANG: -GỬI HÀNG XE VÕ MINH 0383 577268</t>
         </is>
       </c>
     </row>
@@ -527,12 +527,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FNYMCN0011</t>
+          <t>FGCQAA0012.1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NYMAX (Kiện 150 hộp x 1 vỉ x 10 viên)</t>
+          <t>TÍCH ĐIỂM_GINKGO 150 COQ10 ABIPHA - MẪU 2 (Kiện 80 Hộp 10 vỉ x 10 viên)</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -540,7 +540,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TÂN DƯỢC</t>
+          <t>MẪU MỚI_N1 TPCN</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -580,20 +580,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FFERAA0012.1</t>
+          <t>FGCQAA0012</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TÍCH ĐIỂM_FEROBIPHA - MẪU 2 (Kiện 105 hộp x 6 vỉ x 10 viên)</t>
+          <t>GINKGO 150 COQ10 ABIPHA - MẪU 2 (Kiện 80 Hộp 10 vỉ x 10 viên)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>46000</v>
+        <v>75000</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+          <t>MẪU MỚI_N1 TPCN</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -603,22 +603,22 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>230000</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>230000</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -633,20 +633,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FFERAA0012</t>
+          <t>FEURAA0022.1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FEROBIPHA - MẪU 2 (Kiện 105 hộp x 6 vỉ x 10 viên)</t>
+          <t>TÍCH ĐIỂM_EUROSCA FORT - MẪU2 (Kiện 100 hộp x 10 vỉ x 10 viên)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46000</v>
+        <v>56000</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+          <t>MẪU MỚI_N1 TPCN</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -686,20 +686,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FBGAAA0013.1</t>
+          <t>FEURAA0022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TÍCH ĐIỂM_BỔ GAN ABIPHA - MẪU 2 (Kiện 100 hộp x 1 túi x 5 vỉ x 10 viên)</t>
+          <t>EUROSCA FORT - MẪU2 (Kiện 100 hộp x 10 vỉ x 10 viên)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>65000</v>
+        <v>56000</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+          <t>MẪU MỚI_N1 TPCN</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -739,20 +739,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FBGAAA0013</t>
+          <t>FFERAA0012.1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BỔ GAN ABIPHA - MẪU 2 (Kiện 100 hộp x 1 túi x 5 vỉ x 10 viên)</t>
+          <t>TÍCH ĐIỂM_FEROBIPHA - MẪU 2 (Kiện 105 hộp x 6 vỉ x 10 viên)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>65000</v>
+        <v>46000</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+          <t>MẪU MỚI_N1 TPCN</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -792,20 +792,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FCALAA0013.1</t>
+          <t>FFERAA0012</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TÍCH ĐIỂM_CALCI D3 - MẪU 2 (Kiện 100 hộp x 6 vỉ x 10 viên)</t>
+          <t>FEROBIPHA - MẪU 2 (Kiện 105 hộp x 6 vỉ x 10 viên)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>48000</v>
+        <v>46000</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+          <t>MẪU MỚI_N1 TPCN</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -815,22 +815,22 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2400000</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2400000</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -845,12 +845,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FCALAA0013</t>
+          <t>FCALAA0013.1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CALCI D3 - MẪU 2 (Kiện 100 hộp x 6 vỉ x 10 viên)</t>
+          <t>TÍCH ĐIỂM_CALCI D3 - MẪU 2 (Kiện 100 hộp x 6 vỉ x 10 viên)</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -858,7 +858,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+          <t>MẪU MỚI_N1 TPCN</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -898,20 +898,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FENTAA0021</t>
+          <t>FCALAA0013</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Enterome Gold (Kiện 60 hộp x 4 vỉ x 5 ống x 5ml)</t>
+          <t>CALCI D3 - MẪU 2 (Kiện 100 hộp x 6 vỉ x 10 viên)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>96000</v>
+        <v>48000</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 2_TPCN</t>
+          <t>MẪU MỚI_N1 TPCN</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -921,22 +921,22 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>480000</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>480000</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -951,20 +951,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FEURAA0022</t>
+          <t>FBGAAA0013.1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EUROSCA FORT - MẪU2 (Kiện 100 hộp x 10 vỉ x 10 viên)</t>
+          <t>TÍCH ĐIỂM_BỔ GAN ABIPHA - MẪU 2 (Kiện 100 hộp x 1 túi x 5 vỉ x 10 viên)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>56000</v>
+        <v>65000</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+          <t>MẪU MỚI_N1 TPCN</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1004,20 +1004,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FEURAA0022.1</t>
+          <t>FBGAAA0013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TÍCH ĐIỂM_EUROSCA FORT - MẪU2 (Kiện 100 hộp x 10 vỉ x 10 viên)</t>
+          <t>BỔ GAN ABIPHA - MẪU 2 (Kiện 100 hộp x 1 túi x 5 vỉ x 10 viên)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>56000</v>
+        <v>65000</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+          <t>MẪU MỚI_N1 TPCN</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1057,20 +1057,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FVEAAA0012</t>
+          <t>FNYMCN0011</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VITAMIN E ABIPHA - MẪU 2 (Kiện 100 hộp x 1 túi x 3 vỉ x 10 viên)</t>
+          <t>NYMAX (Kiện 150 hộp x 1 vỉ x 10 viên)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>29000</v>
+        <v>75000</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+          <t>N1_TÂN DƯỢC</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1110,73 +1110,73 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FVEAAA0012.1</t>
+          <t>FENTAA0021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TÍCH ĐIỂM_VITAMIN E ABIPHA - MẪU 2 (Kiện 100 hộp x 1 túi x 3 vỉ x 10 viên)</t>
+          <t>Enterome Gold (Kiện 60 hộp x 4 vỉ x 5 ống x 5ml)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29000</v>
+        <v>96000</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+          <t>N2_TPCN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1920000</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>480000</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1920000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FVITAA0022</t>
+          <t>FVEAAA0012</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>VITAMIN 3B ABI - MẪU 2 (Kiện 80 hộp 10 vỉ x 10 viên)</t>
+          <t>VITAMIN E ABIPHA - MẪU 2 (Kiện 100 hộp x 1 túi x 3 vỉ x 10 viên)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>56000</v>
+        <v>29000</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+          <t>MẪU MỚI_N1 TPCN</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1216,20 +1216,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FVITAA0022.1</t>
+          <t>FVEAAA0012.1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TÍCH ĐIỂM_VITAMIN 3B ABI - MẪU 2 (Kiện 80 hộp 10 vỉ x 10 viên)</t>
+          <t>TÍCH ĐIỂM_VITAMIN E ABIPHA - MẪU 2 (Kiện 100 hộp x 1 túi x 3 vỉ x 10 viên)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>56000</v>
+        <v>29000</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+          <t>MẪU MỚI_N1 TPCN</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1239,13 +1239,13 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2900000</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1257,32 +1257,32 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2900000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FVADAA0013.1</t>
+          <t>FVITAA0022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TÍCH ĐIỂM_VITAMIN A-D - MẪU 2 (Kiện 100 hộp x10 vỉ x 10 viên)</t>
+          <t>VITAMIN 3B ABI - MẪU 2 (Kiện 80 hộp 10 vỉ x 10 viên)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>36000</v>
+        <v>56000</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+          <t>MẪU MỚI_N1 TPCN</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1322,20 +1322,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FSANAA0012.1</t>
+          <t>FVITAA0022.1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TÍCH ĐIỂM_SIRO ĂN NGON ABIPHA - MẪU 2 (Kiện 60 hộp x 1 lọ 125ml)</t>
+          <t>TÍCH ĐIỂM_VITAMIN 3B ABI - MẪU 2 (Kiện 80 hộp 10 vỉ x 10 viên)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>48000</v>
+        <v>56000</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+          <t>MẪU MỚI_N1 TPCN</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1345,13 +1345,13 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>3920000</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1363,24 +1363,24 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3920000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FVADAA0013</t>
+          <t>FVADAA0013.1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VITAMIN A-D - MẪU 2 (Kiện 100 hộp x10 vỉ x 10 viên)</t>
+          <t>TÍCH ĐIỂM_VITAMIN A-D - MẪU 2 (Kiện 100 hộp x10 vỉ x 10 viên)</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+          <t>MẪU MỚI_N1 TPCN</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1398,42 +1398,42 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>3600000</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3420000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FSANAA0012</t>
+          <t>FSANAA0012.1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SIRO ĂN NGON ABIPHA - MẪU 2 (Kiện 60 hộp x 1 lọ 125ml)</t>
+          <t>TÍCH ĐIỂM_SIRO ĂN NGON ABIPHA - MẪU 2 (Kiện 60 hộp x 1 lọ 125ml)</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+          <t>MẪU MỚI_N1 TPCN</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1481,20 +1481,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FGCQAA0012.1</t>
+          <t>FVADAA0013</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TÍCH ĐIỂM_GINKGO 150 COQ10 ABIPHA - MẪU 2 (Kiện 80 Hộp 10 vỉ x 10 viên)</t>
+          <t>VITAMIN A-D - MẪU 2 (Kiện 100 hộp x10 vỉ x 10 viên)</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>75000</v>
+        <v>36000</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+          <t>MẪU MỚI_N1 TPCN</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1504,22 +1504,22 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>15750000</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>15750000</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -1534,20 +1534,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FGCQAA0012</t>
+          <t>FSANAA0012</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GINKGO 150 COQ10 ABIPHA - MẪU 2 (Kiện 80 Hộp 10 vỉ x 10 viên)</t>
+          <t>SIRO ĂN NGON ABIPHA - MẪU 2 (Kiện 60 hộp x 1 lọ 125ml)</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>75000</v>
+        <v>48000</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MẪU MỚI_Nhóm hàng hóa 1 TPCN</t>
+          <t>MẪU MỚI_N1 TPCN</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1557,28 +1557,28 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -1600,41 +1600,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="F25" t="n">
-        <v>-32</v>
+        <v>21</v>
       </c>
       <c r="G25" t="n">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="H25" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I25" t="n">
-        <v>9240000</v>
+        <v>8120000</v>
       </c>
       <c r="J25" t="n">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="K25" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L25" t="n">
-        <v>8120000</v>
+        <v>7336000</v>
       </c>
       <c r="M25" t="n">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="N25" t="n">
-        <v>-28</v>
+        <v>24</v>
       </c>
       <c r="O25" t="n">
-        <v>2240000</v>
+        <v>6552000</v>
       </c>
     </row>
     <row r="26">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+          <t>N1_THUỐC DD DÁN TEM</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+          <t>N1_THUỐC DD</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1759,41 +1759,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 2_TPCN</t>
+          <t>N2_TPCN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H28" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I28" t="n">
-        <v>9440000</v>
+        <v>7080000</v>
       </c>
       <c r="J28" t="n">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="K28" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L28" t="n">
-        <v>9440000</v>
+        <v>1770000</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>7080000</v>
       </c>
     </row>
     <row r="29">
@@ -1812,14 +1812,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TÂN DƯỢC</t>
+          <t>N1_TÂN DƯỢC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1831,22 +1831,22 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>177000</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1534000</v>
       </c>
     </row>
     <row r="30">
@@ -1865,41 +1865,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G30" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="H30" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I30" t="n">
-        <v>3220000</v>
+        <v>4600000</v>
       </c>
       <c r="J30" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="K30" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L30" t="n">
-        <v>3220000</v>
+        <v>1150000</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>8280000</v>
       </c>
     </row>
     <row r="31">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+          <t>N1_THUỐC DD</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -2024,20 +2024,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -2046,19 +2046,19 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N33" t="n">
-        <v>11</v>
+        <v>-3</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1590000</v>
       </c>
     </row>
     <row r="34">
@@ -2077,14 +2077,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+          <t>N1_THUỐC DD</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F34" t="n">
-        <v>-11</v>
+        <v>12</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -2105,13 +2105,13 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N34" t="n">
-        <v>-11</v>
+        <v>12</v>
       </c>
       <c r="O34" t="n">
-        <v>180000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="35">
@@ -2130,41 +2130,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F35" t="n">
-        <v>-26</v>
+        <v>7</v>
       </c>
       <c r="G35" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="H35" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I35" t="n">
-        <v>5110000</v>
+        <v>1460000</v>
       </c>
       <c r="J35" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="K35" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L35" t="n">
-        <v>3285000</v>
+        <v>1460000</v>
       </c>
       <c r="M35" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="N35" t="n">
-        <v>-21</v>
+        <v>7</v>
       </c>
       <c r="O35" t="n">
-        <v>2555000</v>
+        <v>2117000</v>
       </c>
     </row>
     <row r="36">
@@ -2183,41 +2183,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+          <t>N1_THUỐC DD DÁN TEM</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>2670000</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3115000</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1602000</v>
       </c>
     </row>
     <row r="37">
@@ -2236,41 +2236,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1800000</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1440000</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2790000</v>
       </c>
     </row>
     <row r="38">
@@ -2289,41 +2289,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G38" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I38" t="n">
-        <v>600000</v>
+        <v>4200000</v>
       </c>
       <c r="J38" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K38" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L38" t="n">
-        <v>600000</v>
+        <v>2400000</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3660000</v>
       </c>
     </row>
     <row r="39">
@@ -2342,14 +2342,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="F39" t="n">
-        <v>-75</v>
+        <v>33</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -2361,22 +2361,22 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2240000</v>
       </c>
       <c r="M39" t="n">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="N39" t="n">
-        <v>-75</v>
+        <v>26</v>
       </c>
       <c r="O39" t="n">
-        <v>1680000</v>
+        <v>4816000</v>
       </c>
     </row>
     <row r="40">
@@ -2395,41 +2395,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 2_TPCN</t>
+          <t>N2_TPCN</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>6480000</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>4536000</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>4104000</v>
       </c>
     </row>
     <row r="41">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+          <t>N1_THUỐC DD</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -2501,41 +2501,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G42" t="n">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="H42" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="I42" t="n">
-        <v>525000</v>
+        <v>6300000</v>
       </c>
       <c r="J42" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="K42" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="L42" t="n">
-        <v>525000</v>
+        <v>3150000</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>7455000</v>
       </c>
     </row>
     <row r="43">
@@ -2554,41 +2554,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 2_TPCN</t>
+          <t>N2_TPCN</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="H43" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I43" t="n">
-        <v>7812000</v>
+        <v>5580000</v>
       </c>
       <c r="J43" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="K43" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L43" t="n">
-        <v>7812000</v>
+        <v>2790000</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3534000</v>
       </c>
     </row>
     <row r="44">
@@ -2607,41 +2607,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>5600000</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>3360000</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>9856000</v>
       </c>
     </row>
     <row r="45">
@@ -2660,14 +2660,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+          <t>N1_THUỐC DD</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2688,13 +2688,13 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>5460000</v>
       </c>
     </row>
     <row r="46">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -2766,41 +2766,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>7600000</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>3990000</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>10830000</v>
       </c>
     </row>
     <row r="48">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TÂN DƯỢC</t>
+          <t>N1_TÂN DƯỢC</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -2935,22 +2935,22 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>495000</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>495000</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -2978,41 +2978,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+          <t>N1_THUỐC DD DÁN TEM</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>21000000</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>18375000</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>10290000</v>
       </c>
     </row>
     <row r="52">
@@ -3031,41 +3031,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+          <t>N1_THUỐC DD DÁN TEM</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>2370000</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>3397000</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>1106000</v>
       </c>
     </row>
     <row r="53">
@@ -3084,41 +3084,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+          <t>N1_THUỐC DD DÁN TEM</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>5900000</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>4720000</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3776000</v>
       </c>
     </row>
     <row r="54">
@@ -3137,41 +3137,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+          <t>N1_THUỐC DD DÁN TEM</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3</v>
+        <v>166</v>
       </c>
       <c r="F54" t="n">
-        <v>-3</v>
+        <v>-18</v>
       </c>
       <c r="G54" t="n">
-        <v>42</v>
+        <v>200</v>
       </c>
       <c r="H54" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I54" t="n">
-        <v>2520000</v>
+        <v>12000000</v>
       </c>
       <c r="J54" t="n">
-        <v>42</v>
+        <v>226</v>
       </c>
       <c r="K54" t="n">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="L54" t="n">
-        <v>2520000</v>
+        <v>13560000</v>
       </c>
       <c r="M54" t="n">
-        <v>3</v>
+        <v>140</v>
       </c>
       <c r="N54" t="n">
-        <v>-3</v>
+        <v>-48</v>
       </c>
       <c r="O54" t="n">
-        <v>180000</v>
+        <v>8400000</v>
       </c>
     </row>
     <row r="55">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+          <t>N1_THUỐC DD DÁN TEM</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -3243,41 +3243,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G56" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>3960000</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="K56" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="L56" t="n">
-        <v>3960000</v>
+        <v>2268000</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>360000</v>
       </c>
     </row>
     <row r="57">
@@ -3296,41 +3296,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 2_TPCN</t>
+          <t>N2_TPCN</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>7840000</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>3920000</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>5292000</v>
       </c>
     </row>
     <row r="58">
@@ -3349,23 +3349,23 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>780000</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3377,13 +3377,13 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>858000</v>
       </c>
     </row>
     <row r="59">
@@ -3402,14 +3402,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -3421,22 +3421,22 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="60">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -3561,41 +3561,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G62" t="n">
+        <v>50</v>
+      </c>
+      <c r="H62" t="n">
         <v>10</v>
       </c>
-      <c r="H62" t="n">
-        <v>2</v>
-      </c>
       <c r="I62" t="n">
-        <v>460000</v>
+        <v>2300000</v>
       </c>
       <c r="J62" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="K62" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L62" t="n">
-        <v>460000</v>
+        <v>2484000</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>2530000</v>
       </c>
     </row>
     <row r="63">
@@ -3614,41 +3614,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 2_TPCN</t>
+          <t>N2_TPCN</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1600000</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>2080000</v>
       </c>
     </row>
     <row r="64">
@@ -3667,14 +3667,14 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+          <t>N1_THUỐC DD</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -3695,13 +3695,13 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>735000</v>
       </c>
     </row>
     <row r="65">
@@ -3720,41 +3720,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 2_TPCN</t>
+          <t>N2_TPCN</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G65" t="n">
-        <v>175</v>
+        <v>20</v>
       </c>
       <c r="H65" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="I65" t="n">
-        <v>18900000</v>
+        <v>2160000</v>
       </c>
       <c r="J65" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>18900000</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>6372000</v>
       </c>
     </row>
     <row r="66">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -3879,14 +3879,14 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+          <t>N1_THUỐC DD</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -3907,13 +3907,13 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>825000</v>
       </c>
     </row>
     <row r="69">
@@ -3932,41 +3932,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G69" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H69" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I69" t="n">
-        <v>600000</v>
+        <v>1200000</v>
       </c>
       <c r="J69" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="K69" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L69" t="n">
-        <v>400000</v>
+        <v>1080000</v>
       </c>
       <c r="M69" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="N69" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O69" t="n">
-        <v>200000</v>
+        <v>1640000</v>
       </c>
     </row>
     <row r="70">
@@ -3985,23 +3985,23 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+          <t>N1_THUỐC DD</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>790000</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -4013,13 +4013,13 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>-395000</v>
       </c>
     </row>
     <row r="71">
@@ -4038,41 +4038,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>-4</v>
+        <v>165</v>
       </c>
       <c r="F71" t="n">
-        <v>-4</v>
+        <v>34</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>4800000</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>4560000</v>
       </c>
       <c r="M71" t="n">
-        <v>-4</v>
+        <v>170</v>
       </c>
       <c r="N71" t="n">
-        <v>-4</v>
+        <v>37</v>
       </c>
       <c r="O71" t="n">
-        <v>-192000</v>
+        <v>8160000</v>
       </c>
     </row>
     <row r="72">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -4101,22 +4101,22 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>950000</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>950000</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -4144,14 +4144,14 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+          <t>N1_THUỐC DD</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F73" t="n">
-        <v>-24</v>
+        <v>4</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -4172,13 +4172,13 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="N73" t="n">
-        <v>-24</v>
+        <v>4</v>
       </c>
       <c r="O73" t="n">
-        <v>288000</v>
+        <v>960000</v>
       </c>
     </row>
     <row r="74">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -4250,14 +4250,14 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 2_TPCN</t>
+          <t>N2_TPCN</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -4278,13 +4278,13 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>882000</v>
       </c>
     </row>
     <row r="76">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+          <t>N1_THUỐC DD</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -4409,41 +4409,41 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 2_TPCN</t>
+          <t>N2_TPCN</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G78" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H78" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I78" t="n">
-        <v>1170000</v>
+        <v>3120000</v>
       </c>
       <c r="J78" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K78" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L78" t="n">
-        <v>780000</v>
+        <v>2340000</v>
       </c>
       <c r="M78" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="N78" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O78" t="n">
-        <v>390000</v>
+        <v>2106000</v>
       </c>
     </row>
     <row r="79">
@@ -4462,41 +4462,41 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>20</v>
+        <v>219</v>
       </c>
       <c r="F79" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="G79" t="n">
-        <v>85</v>
+        <v>800</v>
       </c>
       <c r="H79" t="n">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="I79" t="n">
-        <v>3060000</v>
+        <v>28800000</v>
       </c>
       <c r="J79" t="n">
-        <v>85</v>
+        <v>567</v>
       </c>
       <c r="K79" t="n">
-        <v>17</v>
+        <v>110</v>
       </c>
       <c r="L79" t="n">
-        <v>3060000</v>
+        <v>20412000</v>
       </c>
       <c r="M79" t="n">
-        <v>20</v>
+        <v>452</v>
       </c>
       <c r="N79" t="n">
-        <v>4</v>
+        <v>97</v>
       </c>
       <c r="O79" t="n">
-        <v>720000</v>
+        <v>16272000</v>
       </c>
     </row>
     <row r="80">
@@ -4515,41 +4515,41 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>1200000</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>1200000</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N80" t="n">
         <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>-48000</v>
       </c>
     </row>
     <row r="81">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+          <t>N1_THUỐC DD</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+          <t>N1_THUỐC DD</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -4674,41 +4674,41 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G83" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="H83" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I83" t="n">
-        <v>2160000</v>
+        <v>4800000</v>
       </c>
       <c r="J83" t="n">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="K83" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L83" t="n">
-        <v>2160000</v>
+        <v>3888000</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>5952000</v>
       </c>
     </row>
     <row r="84">
@@ -4727,41 +4727,41 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 2_TPCN</t>
+          <t>N2_TPCN</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
         <v>10</v>
       </c>
-      <c r="H84" t="n">
+      <c r="N84" t="n">
         <v>2</v>
       </c>
-      <c r="I84" t="n">
+      <c r="O84" t="n">
         <v>920000</v>
-      </c>
-      <c r="J84" t="n">
-        <v>10</v>
-      </c>
-      <c r="K84" t="n">
-        <v>2</v>
-      </c>
-      <c r="L84" t="n">
-        <v>920000</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -4780,14 +4780,14 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+          <t>N1_THUỐC DD</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -4808,13 +4808,13 @@
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>3480000</v>
       </c>
     </row>
     <row r="86">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -4886,41 +4886,41 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>-1</v>
+        <v>82</v>
       </c>
       <c r="F87" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="G87" t="n">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="H87" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="I87" t="n">
-        <v>1125000</v>
+        <v>10125000</v>
       </c>
       <c r="J87" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="K87" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L87" t="n">
-        <v>1125000</v>
+        <v>4800000</v>
       </c>
       <c r="M87" t="n">
-        <v>-1</v>
+        <v>153</v>
       </c>
       <c r="N87" t="n">
-        <v>-1</v>
+        <v>33</v>
       </c>
       <c r="O87" t="n">
-        <v>-75000</v>
+        <v>11475000</v>
       </c>
     </row>
     <row r="88">
@@ -4939,41 +4939,41 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>480000</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>480000</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N88" t="n">
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="89">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+          <t>N1_THUỐC DD</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -5045,41 +5045,41 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G90" t="n">
-        <v>5</v>
+        <v>150</v>
       </c>
       <c r="H90" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="I90" t="n">
-        <v>375000</v>
+        <v>11250000</v>
       </c>
       <c r="J90" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="K90" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L90" t="n">
-        <v>375000</v>
+        <v>3375000</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>21000000</v>
       </c>
     </row>
     <row r="91">
@@ -5098,41 +5098,41 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>-16</v>
+        <v>103</v>
       </c>
       <c r="F91" t="n">
-        <v>-8</v>
+        <v>20</v>
       </c>
       <c r="G91" t="n">
-        <v>510</v>
+        <v>300</v>
       </c>
       <c r="H91" t="n">
-        <v>102</v>
+        <v>60</v>
       </c>
       <c r="I91" t="n">
-        <v>40800000</v>
+        <v>24000000</v>
       </c>
       <c r="J91" t="n">
-        <v>490</v>
+        <v>115</v>
       </c>
       <c r="K91" t="n">
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="L91" t="n">
-        <v>39200000</v>
+        <v>9200000</v>
       </c>
       <c r="M91" t="n">
-        <v>4</v>
+        <v>288</v>
       </c>
       <c r="N91" t="n">
-        <v>-4</v>
+        <v>57</v>
       </c>
       <c r="O91" t="n">
-        <v>320000</v>
+        <v>23040000</v>
       </c>
     </row>
     <row r="92">
@@ -5151,41 +5151,41 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G92" t="n">
-        <v>5</v>
+        <v>130</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="I92" t="n">
-        <v>325000</v>
+        <v>8450000</v>
       </c>
       <c r="J92" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L92" t="n">
-        <v>325000</v>
+        <v>5005000</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>6500000</v>
       </c>
     </row>
     <row r="93">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -5276,22 +5276,22 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>340000</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>340000</v>
       </c>
     </row>
     <row r="95">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 2_TPCN</t>
+          <t>N2_TPCN</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -5320,22 +5320,22 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>30090000</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>30090000</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
@@ -5363,14 +5363,14 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -5391,13 +5391,13 @@
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>1513000</v>
       </c>
     </row>
     <row r="97">
@@ -5416,41 +5416,41 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>-12</v>
+        <v>77</v>
       </c>
       <c r="F97" t="n">
-        <v>-12</v>
+        <v>15</v>
       </c>
       <c r="G97" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H97" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I97" t="n">
-        <v>900000</v>
+        <v>2700000</v>
       </c>
       <c r="J97" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="K97" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L97" t="n">
-        <v>450000</v>
+        <v>2475000</v>
       </c>
       <c r="M97" t="n">
-        <v>-2</v>
+        <v>82</v>
       </c>
       <c r="N97" t="n">
-        <v>-10</v>
+        <v>16</v>
       </c>
       <c r="O97" t="n">
-        <v>-90000</v>
+        <v>3690000</v>
       </c>
     </row>
     <row r="98">
@@ -5469,14 +5469,14 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+          <t>N1_THUỐC DD</t>
         </is>
       </c>
       <c r="E98" t="n">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -5500,7 +5500,7 @@
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -5522,14 +5522,14 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -5541,22 +5541,22 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>78000</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>429000</v>
       </c>
     </row>
     <row r="100">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -5628,41 +5628,41 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TÂN DƯỢC</t>
+          <t>N1_TÂN DƯỢC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>340000</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K101" t="n">
         <v>1</v>
       </c>
       <c r="L101" t="n">
-        <v>340000</v>
+        <v>612000</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N101" t="n">
         <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>952000</v>
       </c>
     </row>
     <row r="102">
@@ -5681,14 +5681,14 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 2_TPCN</t>
+          <t>N2_TPCN</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G102" t="n">
         <v>40</v>
@@ -5700,22 +5700,22 @@
         <v>5520000</v>
       </c>
       <c r="J102" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="K102" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L102" t="n">
-        <v>5520000</v>
+        <v>2070000</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>6624000</v>
       </c>
     </row>
     <row r="103">
@@ -5734,41 +5734,41 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G103" t="n">
-        <v>50</v>
+        <v>280</v>
       </c>
       <c r="H103" t="n">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="I103" t="n">
-        <v>3750000</v>
+        <v>21000000</v>
       </c>
       <c r="J103" t="n">
-        <v>50</v>
+        <v>256</v>
       </c>
       <c r="K103" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L103" t="n">
-        <v>3750000</v>
+        <v>19200000</v>
       </c>
       <c r="M103" t="n">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="N103" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="O103" t="n">
-        <v>750000</v>
+        <v>6450000</v>
       </c>
     </row>
     <row r="104">
@@ -5787,14 +5787,14 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -5806,22 +5806,22 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>920000</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
+        <v>1748000</v>
       </c>
     </row>
     <row r="105">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -5893,41 +5893,41 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 2_TPCN</t>
+          <t>N2_TPCN</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G106" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H106" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I106" t="n">
-        <v>3348000</v>
+        <v>3720000</v>
       </c>
       <c r="J106" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K106" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L106" t="n">
-        <v>3348000</v>
+        <v>2790000</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>4650000</v>
       </c>
     </row>
     <row r="107">
@@ -5946,41 +5946,41 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TÂN DƯỢC</t>
+          <t>N1_TÂN DƯỢC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F107" t="n">
-        <v>-8</v>
+        <v>3</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>3960000</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K107" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2772000</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="N107" t="n">
-        <v>-8</v>
+        <v>3</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
+        <v>7326000</v>
       </c>
     </row>
     <row r="108">
@@ -5999,41 +5999,41 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 2_TPCN</t>
+          <t>N2_TPCN</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>4080000</v>
       </c>
       <c r="J108" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K108" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2992000</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O108" t="n">
-        <v>0</v>
+        <v>2856000</v>
       </c>
     </row>
     <row r="109">
@@ -6052,41 +6052,41 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>11700000</v>
       </c>
       <c r="J109" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="K109" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>9425000</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>8580000</v>
       </c>
     </row>
     <row r="110">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -6158,14 +6158,14 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 2_TPCN</t>
+          <t>N2_TPCN</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G111" t="n">
         <v>10</v>
@@ -6177,22 +6177,22 @@
         <v>1280000</v>
       </c>
       <c r="J111" t="n">
+        <v>5</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1</v>
+      </c>
+      <c r="L111" t="n">
+        <v>640000</v>
+      </c>
+      <c r="M111" t="n">
         <v>10</v>
       </c>
-      <c r="K111" t="n">
+      <c r="N111" t="n">
         <v>2</v>
       </c>
-      <c r="L111" t="n">
+      <c r="O111" t="n">
         <v>1280000</v>
-      </c>
-      <c r="M111" t="n">
-        <v>0</v>
-      </c>
-      <c r="N111" t="n">
-        <v>0</v>
-      </c>
-      <c r="O111" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -6211,41 +6211,41 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_TPCN</t>
+          <t>N1_TPCN</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G112" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="H112" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I112" t="n">
-        <v>3480000</v>
+        <v>4060000</v>
       </c>
       <c r="J112" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="K112" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="L112" t="n">
-        <v>3480000</v>
+        <v>2610000</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>3277000</v>
       </c>
     </row>
     <row r="113">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD</t>
+          <t>N1_THUỐC DD</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -6317,41 +6317,41 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+          <t>N1_THUỐC DD DÁN TEM</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>825000</v>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>247500</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O114" t="n">
-        <v>0</v>
+        <v>907500</v>
       </c>
     </row>
     <row r="115">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+          <t>N1_THUỐC DD DÁN TEM</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -6423,41 +6423,41 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+          <t>N1_THUỐC DD DÁN TEM</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F116" t="n">
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="H116" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="I116" t="n">
-        <v>144000</v>
+        <v>7680000</v>
       </c>
       <c r="J116" t="n">
-        <v>3</v>
+        <v>93</v>
       </c>
       <c r="K116" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L116" t="n">
-        <v>144000</v>
+        <v>4464000</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
+        <v>4416000</v>
       </c>
     </row>
     <row r="117">
@@ -6476,41 +6476,41 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+          <t>N1_THUỐC DD DÁN TEM</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>1960000</v>
       </c>
       <c r="J117" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1960000</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
+        <v>2646000</v>
       </c>
     </row>
     <row r="118">
@@ -6529,14 +6529,14 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+          <t>N1_THUỐC DD DÁN TEM</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -6548,22 +6548,22 @@
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K118" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>11550000</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>-36</v>
       </c>
       <c r="O118" t="n">
-        <v>0</v>
+        <v>3780000</v>
       </c>
     </row>
     <row r="119">
@@ -6582,41 +6582,41 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+          <t>N1_THUỐC DD DÁN TEM</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
+        <v>1780000</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>3738000</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>1780000</v>
       </c>
     </row>
     <row r="120">
@@ -6635,41 +6635,41 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+          <t>N1_THUỐC DD DÁN TEM</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>7200000</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="K120" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>7440000</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>2760000</v>
       </c>
     </row>
     <row r="121">
@@ -6688,41 +6688,41 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+          <t>N1_THUỐC DD DÁN TEM</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G121" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="H121" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I121" t="n">
-        <v>768000</v>
+        <v>6400000</v>
       </c>
       <c r="J121" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="K121" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="L121" t="n">
-        <v>768000</v>
+        <v>7040000</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>4224000</v>
       </c>
     </row>
     <row r="122">
@@ -6741,41 +6741,41 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Nhóm hàng hóa 1_THUỐC DD DÁN TEM</t>
+          <t>N1_THUỐC DD DÁN TEM</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>18920000</v>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="K122" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>9804000</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>16942000</v>
       </c>
     </row>
     <row r="123">
@@ -6833,7 +6833,7 @@
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="N124" t="n">
         <v>0</v>
